--- a/testCase + дефект.xlsx
+++ b/testCase + дефект.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Степа\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Степа\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62337DFA-8D19-4640-86F7-7730BE5DEDAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47216067-875E-4FA1-95CC-6E491DF8425E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8025" yWindow="3750" windowWidth="31575" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2595" yWindow="4500" windowWidth="31575" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TestPlan" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="45">
   <si>
     <t>JiraTask</t>
   </si>
@@ -131,18 +131,50 @@
   </si>
   <si>
     <t>SHA-003</t>
+  </si>
+  <si>
+    <t>Роли пользователей</t>
+  </si>
+  <si>
+    <t>Roles--004</t>
+  </si>
+  <si>
+    <t>Регистрация пользователей, проверка присвоения роли user по умолчанию и admin через пароль, а также проверка отображения роли</t>
+  </si>
+  <si>
+    <t>Некорректная раздача ролей, все получают одинаковую роль. Роль не отображается и не понятно какая роль</t>
+  </si>
+  <si>
+    <t>Разграничение доступа</t>
+  </si>
+  <si>
+    <t>Roles--005</t>
+  </si>
+  <si>
+    <t>Проверка отказа доступа обычному пользователю в просмотре всех пользователей</t>
+  </si>
+  <si>
+    <t>Обычные пользователи получают доступ к функциям админа</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -382,73 +414,82 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -869,34 +910,34 @@
       <c r="K7" s="6"/>
     </row>
     <row r="8" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="20" t="s">
+      <c r="A8" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="21" t="s">
+      <c r="B8" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="C8" s="21" t="s">
+      <c r="C8" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="D8" s="21" t="s">
+      <c r="D8" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="E8" s="21" t="s">
+      <c r="E8" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="F8" s="21" t="s">
+      <c r="F8" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="G8" s="21" t="s">
+      <c r="G8" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="H8" s="21" t="s">
+      <c r="H8" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="I8" s="21" t="s">
+      <c r="I8" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="J8" s="21" t="s">
+      <c r="J8" s="20" t="s">
         <v>9</v>
       </c>
       <c r="K8" s="8" t="s">
@@ -904,7 +945,7 @@
       </c>
     </row>
     <row r="9" spans="1:11" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="22" t="s">
+      <c r="A9" s="21" t="s">
         <v>34</v>
       </c>
       <c r="B9" s="9" t="s">
@@ -939,7 +980,7 @@
       </c>
     </row>
     <row r="10" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="22" t="s">
+      <c r="A10" s="21" t="s">
         <v>35</v>
       </c>
       <c r="B10" s="13" t="s">
@@ -972,7 +1013,7 @@
       <c r="K10" s="18"/>
     </row>
     <row r="11" spans="1:11" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="22" t="s">
+      <c r="A11" s="21" t="s">
         <v>36</v>
       </c>
       <c r="B11" s="13" t="s">
@@ -1002,28 +1043,96 @@
       <c r="J11" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="K11" s="19"/>
-    </row>
-    <row r="12" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="15" t="s">
+      <c r="K11" s="25"/>
+    </row>
+    <row r="12" spans="1:11" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="22" t="s">
+        <v>38</v>
+      </c>
+      <c r="B12" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="C12" s="14">
+        <v>1</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="E12" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="F12" s="23" t="s">
+        <v>40</v>
+      </c>
+      <c r="G12" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="H12" s="23" t="s">
+        <v>25</v>
+      </c>
+      <c r="I12" s="23" t="s">
+        <v>25</v>
+      </c>
+      <c r="J12" s="23" t="s">
+        <v>25</v>
+      </c>
+      <c r="K12" s="25"/>
+    </row>
+    <row r="13" spans="1:11" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="B13" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="C13" s="14">
+        <v>1</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="E13" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="F13" s="23" t="s">
+        <v>44</v>
+      </c>
+      <c r="G13" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="H13" s="23" t="s">
+        <v>25</v>
+      </c>
+      <c r="I13" s="23" t="s">
+        <v>25</v>
+      </c>
+      <c r="J13" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="K13" s="24"/>
+    </row>
+    <row r="14" spans="1:11" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="B12" s="16"/>
-      <c r="C12" s="6"/>
-      <c r="D12" s="12"/>
-      <c r="E12" s="11">
-        <v>1.5</v>
-      </c>
-      <c r="F12" s="12"/>
-      <c r="G12" s="12"/>
-      <c r="H12" s="12"/>
-      <c r="I12" s="12"/>
-      <c r="J12" s="12"/>
-      <c r="K12" s="12"/>
-    </row>
-    <row r="14" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="B14" s="16"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="12"/>
+      <c r="E14" s="11">
+        <v>2.5</v>
+      </c>
+      <c r="F14" s="12"/>
+      <c r="G14" s="12"/>
+      <c r="H14" s="12"/>
+      <c r="I14" s="12"/>
+      <c r="J14" s="12"/>
+      <c r="K14" s="12"/>
+    </row>
     <row r="21" ht="30.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="K11:K13"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="0" orientation="portrait" horizontalDpi="0" verticalDpi="0" copies="0"/>
 </worksheet>

--- a/testCase + дефект.xlsx
+++ b/testCase + дефект.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10526"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Степа\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vlov3r/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47216067-875E-4FA1-95CC-6E491DF8425E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08C1C030-97C4-2C43-98F6-082409C7A10C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2595" yWindow="4500" windowWidth="31575" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="2660" windowWidth="28800" windowHeight="15340" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TestPlan" sheetId="1" r:id="rId1"/>
@@ -485,10 +485,10 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -796,19 +796,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K21"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.42578125" customWidth="1"/>
-    <col min="2" max="2" width="23.85546875" customWidth="1"/>
-    <col min="4" max="4" width="89.140625" customWidth="1"/>
-    <col min="6" max="6" width="54.7109375" customWidth="1"/>
-    <col min="7" max="7" width="27.5703125" customWidth="1"/>
-    <col min="8" max="8" width="14.5703125" customWidth="1"/>
-    <col min="9" max="9" width="25.85546875" customWidth="1"/>
-    <col min="10" max="10" width="15.5703125" customWidth="1"/>
+    <col min="1" max="1" width="11.5" customWidth="1"/>
+    <col min="2" max="2" width="23.83203125" customWidth="1"/>
+    <col min="4" max="4" width="89.1640625" customWidth="1"/>
+    <col min="6" max="6" width="54.6640625" customWidth="1"/>
+    <col min="7" max="7" width="27.5" customWidth="1"/>
+    <col min="8" max="8" width="14.5" customWidth="1"/>
+    <col min="9" max="9" width="25.83203125" customWidth="1"/>
+    <col min="10" max="10" width="15.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" ht="25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="B1" s="2"/>
       <c r="C1" s="1"/>
@@ -823,7 +823,7 @@
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
     </row>
-    <row r="2" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" ht="18" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
       <c r="B2" s="4" t="s">
         <v>27</v>
@@ -838,7 +838,7 @@
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
     </row>
-    <row r="3" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="5" t="s">
         <v>28</v>
@@ -853,7 +853,7 @@
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
     </row>
-    <row r="4" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -866,7 +866,7 @@
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
     </row>
-    <row r="5" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="5" t="s">
         <v>29</v>
@@ -881,7 +881,7 @@
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
     </row>
-    <row r="6" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
@@ -894,7 +894,7 @@
       <c r="J6" s="1"/>
       <c r="K6" s="1"/>
     </row>
-    <row r="7" spans="1:11" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" ht="33" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" s="6"/>
       <c r="B7" s="7" t="s">
         <v>30</v>
@@ -909,7 +909,7 @@
       <c r="J7" s="6"/>
       <c r="K7" s="6"/>
     </row>
-    <row r="8" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A8" s="19" t="s">
         <v>0</v>
       </c>
@@ -944,7 +944,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" ht="33" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A9" s="21" t="s">
         <v>34</v>
       </c>
@@ -979,7 +979,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" s="21" t="s">
         <v>35</v>
       </c>
@@ -1004,15 +1004,15 @@
       <c r="H10" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="I10" s="12" t="s">
-        <v>23</v>
+      <c r="I10" s="23" t="s">
+        <v>21</v>
       </c>
       <c r="J10" s="12" t="s">
         <v>25</v>
       </c>
       <c r="K10" s="18"/>
     </row>
-    <row r="11" spans="1:11" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A11" s="21" t="s">
         <v>36</v>
       </c>
@@ -1037,15 +1037,15 @@
       <c r="H11" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="I11" s="12" t="s">
+      <c r="I11" s="23" t="s">
         <v>21</v>
       </c>
       <c r="J11" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="K11" s="25"/>
-    </row>
-    <row r="12" spans="1:11" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K11" s="24"/>
+    </row>
+    <row r="12" spans="1:11" ht="33" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A12" s="22" t="s">
         <v>38</v>
       </c>
@@ -1076,9 +1076,9 @@
       <c r="J12" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="K12" s="25"/>
-    </row>
-    <row r="13" spans="1:11" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K12" s="24"/>
+    </row>
+    <row r="13" spans="1:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A13" s="22" t="s">
         <v>42</v>
       </c>
@@ -1109,9 +1109,9 @@
       <c r="J13" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="K13" s="24"/>
-    </row>
-    <row r="14" spans="1:11" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K13" s="25"/>
+    </row>
+    <row r="14" spans="1:11" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A14" s="15" t="s">
         <v>33</v>
       </c>
@@ -1128,7 +1128,7 @@
       <c r="J14" s="12"/>
       <c r="K14" s="12"/>
     </row>
-    <row r="21" ht="30.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="21" ht="30.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="K11:K13"/>
